--- a/data/incorrect-instances_gpt-35.xlsx
+++ b/data/incorrect-instances_gpt-35.xlsx
@@ -8,19 +8,54 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ownCloud\scripts\hil-test-case-gen\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D50E52-C8A4-4761-A1B9-D149873CAC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1E7971-FA0F-413D-B1C6-51B463207381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="109">
   <si>
     <t>idx</t>
   </si>
@@ -326,6 +361,27 @@
   </si>
   <si>
     <t>The vehicle's onboard systems must log steering and acceleration patterns during various traffic scenarios to inform future safety enhancements</t>
+  </si>
+  <si>
+    <t>acceleration_pedal</t>
+  </si>
+  <si>
+    <t>wheel_steering_angle</t>
+  </si>
+  <si>
+    <t>wheel_speed</t>
+  </si>
+  <si>
+    <t>yaw_rate</t>
+  </si>
+  <si>
+    <t>steering_torque</t>
+  </si>
+  <si>
+    <t>PreictedFault</t>
+  </si>
+  <si>
+    <t>TrueFault</t>
   </si>
 </sst>
 </file>
@@ -381,16 +437,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -401,6 +492,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AB6E75F-33A0-451B-A5F4-C15851EF13B5}" name="Table1" displayName="Table1" ref="A1:K62" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:K62" xr:uid="{0AB6E75F-33A0-451B-A5F4-C15851EF13B5}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{48E620B4-7EBF-4341-94F5-C54A745A7F69}" name="idx"/>
+    <tableColumn id="2" xr3:uid="{5508679C-47D6-4E14-B730-8BA3E9105DC2}" name="requirement"/>
+    <tableColumn id="3" xr3:uid="{49D59C67-F432-4E09-8DF0-F7A5406C78CB}" name="true_vector"/>
+    <tableColumn id="4" xr3:uid="{2ED4C8DF-D88A-46B6-8C3F-3DB27BB578DE}" name="ai_response"/>
+    <tableColumn id="5" xr3:uid="{D76DAAEB-1148-4479-A591-DE4BC1528995}" name="pred_vector"/>
+    <tableColumn id="6" xr3:uid="{90855DF5-AE09-45CE-A68C-692F6BA6D58A}" name="accuracy"/>
+    <tableColumn id="7" xr3:uid="{087F7417-86CB-47C0-ADC8-DBD2A8CA5B07}" name="completion_tokens"/>
+    <tableColumn id="8" xr3:uid="{81761669-31E3-4BDB-AEED-678C609964B1}" name="prompt_tokens"/>
+    <tableColumn id="9" xr3:uid="{A77F7B0E-1021-4CC1-A0EA-CD68A5E0382C}" name="total_tokens"/>
+    <tableColumn id="10" xr3:uid="{FAC34452-FF8A-437B-A871-F26AB6F18D56}" name="TrueFault">
+      <calculatedColumnFormula array="1">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C2)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C2,SEARCH("1",C2)+1)/2)," "))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{C39A0DA9-C5B8-4B42-9E89-F3D3F360BA64}" name="PreictedFault">
+      <calculatedColumnFormula array="1">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E2)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E2,SEARCH("1",E2)+1)/2)," "))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -688,15 +803,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="149.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="19.21875" customWidth="1"/>
-    <col min="6" max="9" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -724,8 +845,14 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -753,8 +880,22 @@
       <c r="I2">
         <v>791</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C2)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C2,SEARCH("1",C2)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+      <c r="K2" t="str" cm="1">
+        <f t="array" ref="K2">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E2)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E2,SEARCH("1",E2)+1)/2)," "))</f>
+        <v xml:space="preserve">NA,  </v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>22</v>
       </c>
@@ -782,8 +923,22 @@
       <c r="I3">
         <v>788</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" t="str" cm="1">
+        <f t="array" ref="J3">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C3)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C3,SEARCH("1",C3)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+      <c r="K3" t="str" cm="1">
+        <f t="array" ref="K3">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E3)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E3,SEARCH("1",E3)+1)/2)," "))</f>
+        <v xml:space="preserve">NA,  </v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>23</v>
       </c>
@@ -811,8 +966,22 @@
       <c r="I4">
         <v>787</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" t="str" cm="1">
+        <f t="array" ref="J4">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C4)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C4,SEARCH("1",C4)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+      <c r="K4" t="str" cm="1">
+        <f t="array" ref="K4">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E4)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E4,SEARCH("1",E4)+1)/2)," "))</f>
+        <v xml:space="preserve">NA,  </v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>24</v>
       </c>
@@ -840,8 +1009,22 @@
       <c r="I5">
         <v>789</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" t="str" cm="1">
+        <f t="array" ref="J5">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C5)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C5,SEARCH("1",C5)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+      <c r="K5" t="str" cm="1">
+        <f t="array" ref="K5">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E5)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E5,SEARCH("1",E5)+1)/2)," "))</f>
+        <v xml:space="preserve">NA,  </v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>39</v>
       </c>
@@ -869,8 +1052,22 @@
       <c r="I6">
         <v>787</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" t="str" cm="1">
+        <f t="array" ref="J6">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C6)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C6,SEARCH("1",C6)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K6" t="str" cm="1">
+        <f t="array" ref="K6">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E6)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E6,SEARCH("1",E6)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_speed,  </v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+      <c r="N6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>40</v>
       </c>
@@ -898,8 +1095,16 @@
       <c r="I7">
         <v>790</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" t="str" cm="1">
+        <f t="array" ref="J7">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C7)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C7,SEARCH("1",C7)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K7" t="str" cm="1">
+        <f t="array" ref="K7">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E7)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E7,SEARCH("1",E7)+1)/2)," "))</f>
+        <v xml:space="preserve">NA,  </v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>41</v>
       </c>
@@ -927,8 +1132,16 @@
       <c r="I8">
         <v>793</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" t="str" cm="1">
+        <f t="array" ref="J8">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C8)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C8,SEARCH("1",C8)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K8" t="str" cm="1">
+        <f t="array" ref="K8">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E8)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E8,SEARCH("1",E8)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>43</v>
       </c>
@@ -956,8 +1169,16 @@
       <c r="I9">
         <v>782</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" t="str" cm="1">
+        <f t="array" ref="J9">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C9)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C9,SEARCH("1",C9)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K9" t="str" cm="1">
+        <f t="array" ref="K9">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E9)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E9,SEARCH("1",E9)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>45</v>
       </c>
@@ -985,8 +1206,16 @@
       <c r="I10">
         <v>789</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" t="str" cm="1">
+        <f t="array" ref="J10">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C10)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C10,SEARCH("1",C10)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K10" t="str" cm="1">
+        <f t="array" ref="K10">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E10)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E10,SEARCH("1",E10)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>46</v>
       </c>
@@ -1014,8 +1243,16 @@
       <c r="I11">
         <v>785</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" t="str" cm="1">
+        <f t="array" ref="J11">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C11)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C11,SEARCH("1",C11)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K11" t="str" cm="1">
+        <f t="array" ref="K11">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E11)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E11,SEARCH("1",E11)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>48</v>
       </c>
@@ -1043,8 +1280,16 @@
       <c r="I12">
         <v>790</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" t="str" cm="1">
+        <f t="array" ref="J12">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C12)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C12,SEARCH("1",C12)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K12" t="str" cm="1">
+        <f t="array" ref="K12">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E12)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E12,SEARCH("1",E12)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>49</v>
       </c>
@@ -1072,8 +1317,16 @@
       <c r="I13">
         <v>792</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" t="str" cm="1">
+        <f t="array" ref="J13">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C13)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C13,SEARCH("1",C13)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K13" t="str" cm="1">
+        <f t="array" ref="K13">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E13)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E13,SEARCH("1",E13)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>50</v>
       </c>
@@ -1101,8 +1354,16 @@
       <c r="I14">
         <v>782</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" t="str" cm="1">
+        <f t="array" ref="J14">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C14)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C14,SEARCH("1",C14)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K14" t="str" cm="1">
+        <f t="array" ref="K14">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E14)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E14,SEARCH("1",E14)+1)/2)," "))</f>
+        <v xml:space="preserve">NA,  </v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>51</v>
       </c>
@@ -1130,8 +1391,16 @@
       <c r="I15">
         <v>792</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15" t="str" cm="1">
+        <f t="array" ref="J15">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C15)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C15,SEARCH("1",C15)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K15" t="str" cm="1">
+        <f t="array" ref="K15">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E15)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E15,SEARCH("1",E15)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>52</v>
       </c>
@@ -1159,8 +1428,16 @@
       <c r="I16">
         <v>786</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" t="str" cm="1">
+        <f t="array" ref="J16">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C16)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C16,SEARCH("1",C16)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K16" t="str" cm="1">
+        <f t="array" ref="K16">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E16)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E16,SEARCH("1",E16)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>54</v>
       </c>
@@ -1188,8 +1465,16 @@
       <c r="I17">
         <v>791</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17" t="str" cm="1">
+        <f t="array" ref="J17">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C17)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C17,SEARCH("1",C17)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K17" t="str" cm="1">
+        <f t="array" ref="K17">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E17)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E17,SEARCH("1",E17)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>56</v>
       </c>
@@ -1217,8 +1502,16 @@
       <c r="I18">
         <v>788</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18" t="str" cm="1">
+        <f t="array" ref="J18">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C18)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C18,SEARCH("1",C18)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K18" t="str" cm="1">
+        <f t="array" ref="K18">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E18)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E18,SEARCH("1",E18)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>57</v>
       </c>
@@ -1246,8 +1539,16 @@
       <c r="I19">
         <v>788</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" t="str" cm="1">
+        <f t="array" ref="J19">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C19)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C19,SEARCH("1",C19)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K19" t="str" cm="1">
+        <f t="array" ref="K19">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E19)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E19,SEARCH("1",E19)+1)/2)," "))</f>
+        <v>wheel_steering_angle, steering_torque</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>58</v>
       </c>
@@ -1275,8 +1576,16 @@
       <c r="I20">
         <v>794</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20" t="str" cm="1">
+        <f t="array" ref="J20">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C20)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C20,SEARCH("1",C20)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K20" t="str" cm="1">
+        <f t="array" ref="K20">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E20)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E20,SEARCH("1",E20)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>62</v>
       </c>
@@ -1304,8 +1613,16 @@
       <c r="I21">
         <v>792</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21" t="str" cm="1">
+        <f t="array" ref="J21">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C21)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C21,SEARCH("1",C21)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K21" t="str" cm="1">
+        <f t="array" ref="K21">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E21)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E21,SEARCH("1",E21)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>65</v>
       </c>
@@ -1333,8 +1650,16 @@
       <c r="I22">
         <v>791</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22" t="str" cm="1">
+        <f t="array" ref="J22">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C22)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C22,SEARCH("1",C22)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K22" t="str" cm="1">
+        <f t="array" ref="K22">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E22)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E22,SEARCH("1",E22)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>66</v>
       </c>
@@ -1362,8 +1687,16 @@
       <c r="I23">
         <v>787</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23" t="str" cm="1">
+        <f t="array" ref="J23">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C23)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C23,SEARCH("1",C23)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K23" t="str" cm="1">
+        <f t="array" ref="K23">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E23)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E23,SEARCH("1",E23)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>75</v>
       </c>
@@ -1391,8 +1724,16 @@
       <c r="I24">
         <v>789</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24" t="str" cm="1">
+        <f t="array" ref="J24">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C24)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C24,SEARCH("1",C24)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K24" t="str" cm="1">
+        <f t="array" ref="K24">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E24)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E24,SEARCH("1",E24)+1)/2)," "))</f>
+        <v>wheel_steering_angle, wheel_speed</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>84</v>
       </c>
@@ -1420,8 +1761,16 @@
       <c r="I25">
         <v>795</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25" t="str" cm="1">
+        <f t="array" ref="J25">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C25)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C25,SEARCH("1",C25)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+      <c r="K25" t="str" cm="1">
+        <f t="array" ref="K25">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E25)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E25,SEARCH("1",E25)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>100</v>
       </c>
@@ -1449,8 +1798,16 @@
       <c r="I26">
         <v>789</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26" t="str" cm="1">
+        <f t="array" ref="J26">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C26)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C26,SEARCH("1",C26)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_speed,  </v>
+      </c>
+      <c r="K26" t="str" cm="1">
+        <f t="array" ref="K26">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E26)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E26,SEARCH("1",E26)+1)/2)," "))</f>
+        <v xml:space="preserve">NA,  </v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>110</v>
       </c>
@@ -1478,8 +1835,16 @@
       <c r="I27">
         <v>785</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27" t="str" cm="1">
+        <f t="array" ref="J27">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C27)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C27,SEARCH("1",C27)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_speed,  </v>
+      </c>
+      <c r="K27" t="str" cm="1">
+        <f t="array" ref="K27">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E27)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E27,SEARCH("1",E27)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>126</v>
       </c>
@@ -1507,8 +1872,16 @@
       <c r="I28">
         <v>792</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28" t="str" cm="1">
+        <f t="array" ref="J28">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C28)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C28,SEARCH("1",C28)+1)/2)," "))</f>
+        <v xml:space="preserve">yaw_rate,  </v>
+      </c>
+      <c r="K28" t="str" cm="1">
+        <f t="array" ref="K28">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E28)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E28,SEARCH("1",E28)+1)/2)," "))</f>
+        <v>wheel_steering_angle, wheel_speed</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>127</v>
       </c>
@@ -1536,8 +1909,16 @@
       <c r="I29">
         <v>795</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29" t="str" cm="1">
+        <f t="array" ref="J29">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C29)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C29,SEARCH("1",C29)+1)/2)," "))</f>
+        <v xml:space="preserve">yaw_rate,  </v>
+      </c>
+      <c r="K29" t="str" cm="1">
+        <f t="array" ref="K29">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E29)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E29,SEARCH("1",E29)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>128</v>
       </c>
@@ -1565,8 +1946,16 @@
       <c r="I30">
         <v>785</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30" t="str" cm="1">
+        <f t="array" ref="J30">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C30)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C30,SEARCH("1",C30)+1)/2)," "))</f>
+        <v xml:space="preserve">yaw_rate,  </v>
+      </c>
+      <c r="K30" t="str" cm="1">
+        <f t="array" ref="K30">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E30)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E30,SEARCH("1",E30)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_speed,  </v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>131</v>
       </c>
@@ -1594,8 +1983,16 @@
       <c r="I31">
         <v>785</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31" t="str" cm="1">
+        <f t="array" ref="J31">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C31)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C31,SEARCH("1",C31)+1)/2)," "))</f>
+        <v xml:space="preserve">yaw_rate,  </v>
+      </c>
+      <c r="K31" t="str" cm="1">
+        <f t="array" ref="K31">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E31)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E31,SEARCH("1",E31)+1)/2)," "))</f>
+        <v>wheel_speed, yaw_rate</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>163</v>
       </c>
@@ -1623,8 +2020,16 @@
       <c r="I32">
         <v>788</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32" t="str" cm="1">
+        <f t="array" ref="J32">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C32)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C32,SEARCH("1",C32)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K32" t="str" cm="1">
+        <f t="array" ref="K32">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E32)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E32,SEARCH("1",E32)+1)/2)," "))</f>
+        <v>wheel_speed, steering_torque</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>164</v>
       </c>
@@ -1652,8 +2057,16 @@
       <c r="I33">
         <v>785</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33" t="str" cm="1">
+        <f t="array" ref="J33">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C33)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C33,SEARCH("1",C33)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K33" t="str" cm="1">
+        <f t="array" ref="K33">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E33)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E33,SEARCH("1",E33)+1)/2)," "))</f>
+        <v>wheel_speed, steering_torque</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>165</v>
       </c>
@@ -1681,8 +2094,16 @@
       <c r="I34">
         <v>792</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34" t="str" cm="1">
+        <f t="array" ref="J34">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C34)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C34,SEARCH("1",C34)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K34" t="str" cm="1">
+        <f t="array" ref="K34">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E34)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E34,SEARCH("1",E34)+1)/2)," "))</f>
+        <v>wheel_speed, steering_torque</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>168</v>
       </c>
@@ -1710,8 +2131,16 @@
       <c r="I35">
         <v>786</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35" t="str" cm="1">
+        <f t="array" ref="J35">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C35)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C35,SEARCH("1",C35)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K35" t="str" cm="1">
+        <f t="array" ref="K35">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E35)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E35,SEARCH("1",E35)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>173</v>
       </c>
@@ -1739,8 +2168,16 @@
       <c r="I36">
         <v>790</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36" t="str" cm="1">
+        <f t="array" ref="J36">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C36)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C36,SEARCH("1",C36)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K36" t="str" cm="1">
+        <f t="array" ref="K36">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E36)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E36,SEARCH("1",E36)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>174</v>
       </c>
@@ -1768,8 +2205,16 @@
       <c r="I37">
         <v>788</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37" t="str" cm="1">
+        <f t="array" ref="J37">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C37)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C37,SEARCH("1",C37)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K37" t="str" cm="1">
+        <f t="array" ref="K37">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E37)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E37,SEARCH("1",E37)+1)/2)," "))</f>
+        <v>wheel_steering_angle, wheel_speed</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>178</v>
       </c>
@@ -1797,8 +2242,16 @@
       <c r="I38">
         <v>789</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38" t="str" cm="1">
+        <f t="array" ref="J38">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C38)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C38,SEARCH("1",C38)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K38" t="str" cm="1">
+        <f t="array" ref="K38">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E38)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E38,SEARCH("1",E38)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>179</v>
       </c>
@@ -1826,8 +2279,16 @@
       <c r="I39">
         <v>786</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J39" t="str" cm="1">
+        <f t="array" ref="J39">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C39)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C39,SEARCH("1",C39)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K39" t="str" cm="1">
+        <f t="array" ref="K39">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E39)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E39,SEARCH("1",E39)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>180</v>
       </c>
@@ -1855,8 +2316,16 @@
       <c r="I40">
         <v>789</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J40" t="str" cm="1">
+        <f t="array" ref="J40">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C40)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C40,SEARCH("1",C40)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K40" t="str" cm="1">
+        <f t="array" ref="K40">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E40)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E40,SEARCH("1",E40)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>188</v>
       </c>
@@ -1884,8 +2353,16 @@
       <c r="I41">
         <v>795</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J41" t="str" cm="1">
+        <f t="array" ref="J41">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C41)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C41,SEARCH("1",C41)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K41" t="str" cm="1">
+        <f t="array" ref="K41">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E41)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E41,SEARCH("1",E41)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>192</v>
       </c>
@@ -1913,8 +2390,16 @@
       <c r="I42">
         <v>791</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J42" t="str" cm="1">
+        <f t="array" ref="J42">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C42)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C42,SEARCH("1",C42)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K42" t="str" cm="1">
+        <f t="array" ref="K42">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E42)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E42,SEARCH("1",E42)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>194</v>
       </c>
@@ -1942,8 +2427,16 @@
       <c r="I43">
         <v>789</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J43" t="str" cm="1">
+        <f t="array" ref="J43">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C43)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C43,SEARCH("1",C43)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K43" t="str" cm="1">
+        <f t="array" ref="K43">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E43)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E43,SEARCH("1",E43)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>195</v>
       </c>
@@ -1971,8 +2464,16 @@
       <c r="I44">
         <v>781</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44" t="str" cm="1">
+        <f t="array" ref="J44">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C44)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C44,SEARCH("1",C44)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K44" t="str" cm="1">
+        <f t="array" ref="K44">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E44)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E44,SEARCH("1",E44)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>202</v>
       </c>
@@ -2000,8 +2501,16 @@
       <c r="I45">
         <v>789</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J45" t="str" cm="1">
+        <f t="array" ref="J45">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C45)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C45,SEARCH("1",C45)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K45" t="str" cm="1">
+        <f t="array" ref="K45">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E45)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E45,SEARCH("1",E45)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>206</v>
       </c>
@@ -2029,8 +2538,16 @@
       <c r="I46">
         <v>788</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J46" t="str" cm="1">
+        <f t="array" ref="J46">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C46)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C46,SEARCH("1",C46)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K46" t="str" cm="1">
+        <f t="array" ref="K46">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E46)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E46,SEARCH("1",E46)+1)/2)," "))</f>
+        <v>wheel_steering_angle, wheel_speed</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>207</v>
       </c>
@@ -2058,8 +2575,16 @@
       <c r="I47">
         <v>782</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J47" t="str" cm="1">
+        <f t="array" ref="J47">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C47)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C47,SEARCH("1",C47)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K47" t="str" cm="1">
+        <f t="array" ref="K47">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E47)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E47,SEARCH("1",E47)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>208</v>
       </c>
@@ -2087,8 +2612,16 @@
       <c r="I48">
         <v>787</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J48" t="str" cm="1">
+        <f t="array" ref="J48">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C48)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C48,SEARCH("1",C48)+1)/2)," "))</f>
+        <v xml:space="preserve">steering_torque,  </v>
+      </c>
+      <c r="K48" t="str" cm="1">
+        <f t="array" ref="K48">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E48)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E48,SEARCH("1",E48)+1)/2)," "))</f>
+        <v>wheel_steering_angle, steering_torque</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>212</v>
       </c>
@@ -2116,8 +2649,16 @@
       <c r="I49">
         <v>796</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49" t="str" cm="1">
+        <f t="array" ref="J49">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C49)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C49,SEARCH("1",C49)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K49" t="str" cm="1">
+        <f t="array" ref="K49">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E49)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E49,SEARCH("1",E49)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>217</v>
       </c>
@@ -2145,8 +2686,16 @@
       <c r="I50">
         <v>790</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J50" t="str" cm="1">
+        <f t="array" ref="J50">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C50)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C50,SEARCH("1",C50)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K50" t="str" cm="1">
+        <f t="array" ref="K50">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E50)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E50,SEARCH("1",E50)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>222</v>
       </c>
@@ -2174,8 +2723,16 @@
       <c r="I51">
         <v>792</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51" t="str" cm="1">
+        <f t="array" ref="J51">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C51)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C51,SEARCH("1",C51)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K51" t="str" cm="1">
+        <f t="array" ref="K51">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E51)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E51,SEARCH("1",E51)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -2203,8 +2760,16 @@
       <c r="I52">
         <v>788</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J52" t="str" cm="1">
+        <f t="array" ref="J52">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C52)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C52,SEARCH("1",C52)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K52" t="str" cm="1">
+        <f t="array" ref="K52">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E52)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E52,SEARCH("1",E52)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>229</v>
       </c>
@@ -2232,8 +2797,16 @@
       <c r="I53">
         <v>795</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J53" t="str" cm="1">
+        <f t="array" ref="J53">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C53)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C53,SEARCH("1",C53)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K53" t="str" cm="1">
+        <f t="array" ref="K53">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E53)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E53,SEARCH("1",E53)+1)/2)," "))</f>
+        <v>acceleration_pedal, steering_torque</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>236</v>
       </c>
@@ -2261,8 +2834,16 @@
       <c r="I54">
         <v>790</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J54" t="str" cm="1">
+        <f t="array" ref="J54">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C54)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C54,SEARCH("1",C54)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K54" t="str" cm="1">
+        <f t="array" ref="K54">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E54)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E54,SEARCH("1",E54)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>237</v>
       </c>
@@ -2290,8 +2871,16 @@
       <c r="I55">
         <v>788</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J55" t="str" cm="1">
+        <f t="array" ref="J55">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C55)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C55,SEARCH("1",C55)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K55" t="str" cm="1">
+        <f t="array" ref="K55">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E55)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E55,SEARCH("1",E55)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>238</v>
       </c>
@@ -2319,8 +2908,16 @@
       <c r="I56">
         <v>796</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J56" t="str" cm="1">
+        <f t="array" ref="J56">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C56)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C56,SEARCH("1",C56)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K56" t="str" cm="1">
+        <f t="array" ref="K56">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E56)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E56,SEARCH("1",E56)+1)/2)," "))</f>
+        <v>acceleration_pedal, steering_torque</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>246</v>
       </c>
@@ -2348,8 +2945,16 @@
       <c r="I57">
         <v>793</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J57" t="str" cm="1">
+        <f t="array" ref="J57">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C57)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C57,SEARCH("1",C57)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K57" t="str" cm="1">
+        <f t="array" ref="K57">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E57)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E57,SEARCH("1",E57)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>247</v>
       </c>
@@ -2377,8 +2982,16 @@
       <c r="I58">
         <v>791</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J58" t="str" cm="1">
+        <f t="array" ref="J58">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C58)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C58,SEARCH("1",C58)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K58" t="str" cm="1">
+        <f t="array" ref="K58">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E58)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E58,SEARCH("1",E58)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>248</v>
       </c>
@@ -2406,8 +3019,16 @@
       <c r="I59">
         <v>791</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J59" t="str" cm="1">
+        <f t="array" ref="J59">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C59)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C59,SEARCH("1",C59)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K59" t="str" cm="1">
+        <f t="array" ref="K59">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E59)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E59,SEARCH("1",E59)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>249</v>
       </c>
@@ -2435,8 +3056,16 @@
       <c r="I60">
         <v>795</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J60" t="str" cm="1">
+        <f t="array" ref="J60">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C60)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C60,SEARCH("1",C60)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K60" t="str" cm="1">
+        <f t="array" ref="K60">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E60)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E60,SEARCH("1",E60)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>250</v>
       </c>
@@ -2464,8 +3093,16 @@
       <c r="I61">
         <v>789</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J61" t="str" cm="1">
+        <f t="array" ref="J61">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C61)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C61,SEARCH("1",C61)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K61" t="str" cm="1">
+        <f t="array" ref="K61">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E61)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E61,SEARCH("1",E61)+1)/2)," "))</f>
+        <v xml:space="preserve">wheel_steering_angle,  </v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>252</v>
       </c>
@@ -2493,8 +3130,19 @@
       <c r="I62">
         <v>788</v>
       </c>
+      <c r="J62" t="str" cm="1">
+        <f t="array" ref="J62">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",C62)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",C62,SEARCH("1",C62)+1)/2)," "))</f>
+        <v>acceleration_pedal, wheel_steering_angle</v>
+      </c>
+      <c r="K62" t="str" cm="1">
+        <f t="array" ref="K62">_xlfn.TEXTJOIN(", ",TRUE,IFERROR(INDEX($N$2:$N$6,SEARCH("1",E62)/2),"NA"),IFERROR(INDEX($N$2:$N$6,SEARCH("1",E62,SEARCH("1",E62)+1)/2)," "))</f>
+        <v xml:space="preserve">acceleration_pedal,  </v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>